--- a/Project_ETF/ETF_Investment_Portfolio/00981A/ETF_Investment_Portfolio_20260629.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00981A/ETF_Investment_Portfolio_20260629.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>10.08%</t>
+          <t>10.18%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>9.18%</t>
+          <t>9.37%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>8.49%</t>
+          <t>8.78%</t>
         </is>
       </c>
     </row>
@@ -682,73 +682,73 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>7.04%</t>
+          <t>7.07%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>2,352,000</t>
+          <t>6,334,000</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.51%</t>
+          <t>5.32%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>6,334,000</t>
+          <t>14,735,000</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>5.43%</t>
+          <t>5.16%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>14,735,000</t>
+          <t>2,367,000</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>5.17%</t>
+          <t>5.15%</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>5.11%</t>
+          <t>5.10%</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>4.22%</t>
+          <t>4.29%</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>3.73%</t>
+          <t>3.97%</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>3.66%</t>
+          <t>3.84%</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>3.61%</t>
+          <t>3.46%</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>3.56%</t>
+          <t>3.45%</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>3.23%</t>
+          <t>3.26%</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.90%</t>
+          <t>2.87%</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.88%</t>
+          <t>2.82%</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.78%</t>
+          <t>2.70%</t>
         </is>
       </c>
     </row>
@@ -990,73 +990,73 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>2.13%</t>
+          <t>2.07%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>930,000</t>
+          <t>1,811,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.09%</t>
+          <t>1.06%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>1,811,000</t>
+          <t>2,267,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.07%</t>
+          <t>0.99%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>2,267,000</t>
+          <t>830,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>0.90%</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>0.83%</t>
+          <t>0.81%</t>
         </is>
       </c>
     </row>
@@ -1129,66 +1129,66 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>1,334,000</t>
+          <t>4,481,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>0.52%</t>
+          <t>0.50%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>6147</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>頎邦</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>4,481,000</t>
+          <t>6,275,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>0.50%</t>
+          <t>0.48%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>6147</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>頎邦</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>6,275,000</t>
+          <t>1,334,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.49%</t>
+          <t>0.47%</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.38%</t>
+          <t>0.39%</t>
         </is>
       </c>
     </row>
@@ -1239,39 +1239,39 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>6271</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>同欣電</t>
+          <t>亞德客-KY</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>2,966,000</t>
+          <t>530,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.27%</t>
+          <t>0.26%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>6271</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>亞德客-KY</t>
+          <t>同欣電</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>530,000</t>
+          <t>2,966,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.24%</t>
+          <t>0.25%</t>
         </is>
       </c>
     </row>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.20%</t>
+          <t>0.19%</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.14%</t>
+          <t>0.15%</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>0.12%</t>
+          <t>0.11%</t>
         </is>
       </c>
     </row>
@@ -1437,17 +1437,17 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2439</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>美律</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>18,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -1459,17 +1459,17 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>2481</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>強茂</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>5,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -1481,12 +1481,12 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -1503,17 +1503,17 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>1815</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>富喬</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>107,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -1525,12 +1525,12 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -1547,12 +1547,12 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>世界</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -1569,12 +1569,12 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -1591,12 +1591,12 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -1613,17 +1613,17 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>2481</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>世界</t>
+          <t>強茂</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>5,000</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -1635,12 +1635,12 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -1657,17 +1657,17 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>2439</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>美律</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>18,000</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -1679,17 +1679,17 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>1815</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>富喬</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>107,000</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>6,379,100,584</t>
+          <t>4,442,180,159</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr"/>
@@ -1747,7 +1747,7 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>940,108,533</t>
+          <t>2,810,780,112</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr"/>
